--- a/docs/modules/bsee/data/NPV_JStM-WELL-Production-Data-thru-2019.xlsx
+++ b/docs/modules/bsee/data/NPV_JStM-WELL-Production-Data-thru-2019.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sk Samdan\Desktop\github\worldenergydata\docs\modules\bsee\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\github\worldenergydata\docs\modules\bsee\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEC0EFE-6AD6-4409-B876-F0597E766175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="673" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="673"/>
   </bookViews>
   <sheets>
     <sheet name="NPV w Mo'ly data chart" sheetId="4" r:id="rId1"/>
@@ -22,7 +21,7 @@
     <definedName name="RATE">'NPV w Mo''ly data chart'!$B$32</definedName>
     <definedName name="RecompCOST">'NPV w Mo''ly data chart'!$A$40</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,12 +36,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Charles White</author>
   </authors>
   <commentList>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{E38ED336-C503-4A8F-9084-B2DC7782FE1E}">
+    <comment ref="B8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -66,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{34929368-AD90-4892-9695-E35C5DFE3EF0}">
+    <comment ref="J18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{66176BC9-62D5-4B9F-9001-064FCB91F83E}">
+    <comment ref="G19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -114,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ20" authorId="0" shapeId="0" xr:uid="{2610F9A2-57DA-40F7-8BB1-0ED2CE42DD1E}">
+    <comment ref="AQ20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{DE2FD19A-38A8-4847-A2AF-8218E656E57C}">
+    <comment ref="G27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{BF0CD6A2-3590-4C0A-B6BF-C834BA23A28C}">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -183,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB27" authorId="0" shapeId="0" xr:uid="{AA2878DB-84DC-4E85-8D5A-03AAE0C2569B}">
+    <comment ref="AB27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ27" authorId="0" shapeId="0" xr:uid="{BFE5F762-AC37-46C0-99A0-D5CDE9A910F3}">
+    <comment ref="AQ27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -229,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A36" authorId="0" shapeId="0" xr:uid="{09B3FFD7-6160-49F5-B734-7FAFEFA1F43A}">
+    <comment ref="A36" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -443,17 +442,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -563,6 +562,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -659,26 +664,26 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -693,16 +698,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -729,10 +734,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -744,16 +749,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -771,16 +776,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -789,29 +794,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -825,7 +818,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -845,6 +838,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -873,7 +881,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -912,6 +920,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1331,7 +1340,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -1721,7 +1730,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -2111,7 +2120,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -2126,7 +2135,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> WR678 PS002 </c:v>
+                  <c:v>WR678 PS002</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2501,7 +2510,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -2891,7 +2900,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -3283,7 +3292,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -3675,7 +3684,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -4067,7 +4076,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -4336,7 +4345,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000008-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -4707,7 +4716,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000009-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -5099,7 +5108,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -5492,7 +5501,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000B-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -5885,7 +5894,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000C-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -6275,7 +6284,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000D-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -6665,7 +6674,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000E-C8B7-4FD8-A165-9B2E23958F33}"/>
             </c:ext>
@@ -6680,9 +6689,9 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="544875016"/>
-        <c:axId val="544878952"/>
-        <c:extLst>
+        <c:axId val="-1797192048"/>
+        <c:axId val="-1797199120"/>
+        <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredLineSeries>
               <c15:ser>
@@ -6690,7 +6699,7 @@
                 <c:order val="0"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'NPV w Mo''ly data chart'!$B$4</c15:sqref>
@@ -6904,7 +6913,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'NPV w Mo''ly data chart'!$C$4:$BE$4</c15:sqref>
@@ -7083,7 +7092,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000F-C8B7-4FD8-A165-9B2E23958F33}"/>
                   </c:ext>
@@ -7094,7 +7103,7 @@
         </c:extLst>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="544875016"/>
+        <c:axId val="-1797192048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7137,7 +7146,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="544878952"/>
+        <c:crossAx val="-1797199120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7145,7 +7154,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="544878952"/>
+        <c:axId val="-1797199120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7196,7 +7205,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="544875016"/>
+        <c:crossAx val="-1797192048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7210,6 +7219,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7277,7 +7287,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -7316,6 +7326,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7735,7 +7746,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -8125,7 +8136,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -8515,7 +8526,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -8530,7 +8541,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> WR678 PS002 </c:v>
+                  <c:v>WR678 PS002</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8905,7 +8916,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -9295,7 +9306,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -9687,7 +9698,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -10079,7 +10090,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -10471,7 +10482,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -10740,7 +10751,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000008-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -11111,7 +11122,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000009-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -11503,7 +11514,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -11896,7 +11907,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000B-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -12289,7 +12300,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000C-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -12679,7 +12690,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000D-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -13069,7 +13080,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000E-EF7F-405D-BE05-256CA7A8472B}"/>
             </c:ext>
@@ -13084,9 +13095,9 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="544875016"/>
-        <c:axId val="544878952"/>
-        <c:extLst>
+        <c:axId val="-1797191504"/>
+        <c:axId val="-1797196400"/>
+        <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredLineSeries>
               <c15:ser>
@@ -13094,7 +13105,7 @@
                 <c:order val="0"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'NPV w Mo''ly data chart'!$B$4</c15:sqref>
@@ -13308,7 +13319,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'NPV w Mo''ly data chart'!$C$4:$BE$4</c15:sqref>
@@ -13487,7 +13498,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000F-EF7F-405D-BE05-256CA7A8472B}"/>
                   </c:ext>
@@ -13498,7 +13509,7 @@
         </c:extLst>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="544875016"/>
+        <c:axId val="-1797191504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13541,7 +13552,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="544878952"/>
+        <c:crossAx val="-1797196400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13549,7 +13560,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="544878952"/>
+        <c:axId val="-1797196400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13600,7 +13611,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="544875016"/>
+        <c:crossAx val="-1797191504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13614,6 +13625,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14812,7 +14824,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10533AFC-4D13-464B-8E87-1C3FB5CC6658}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{10533AFC-4D13-464B-8E87-1C3FB5CC6658}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14850,7 +14862,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FDD9C7A-7AE2-46CE-83B8-4732CE20F444}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3FDD9C7A-7AE2-46CE-83B8-4732CE20F444}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14874,9 +14886,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14914,9 +14926,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -14951,7 +14963,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -14986,7 +14998,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15159,43 +15171,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFCEB07-196B-449E-BF09-0A2270B80F8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BI42"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="42" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="44" max="57" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="16" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="16" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="16" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="44" width="16" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="16" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="56" width="16" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:59" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="59"/>
+      <c r="B1" s="55"/>
       <c r="C1" s="41"/>
       <c r="D1" s="35">
         <v>2015</v>
@@ -15262,9 +15293,9 @@
       <c r="BD1" s="35"/>
       <c r="BE1" s="35"/>
     </row>
-    <row r="2" spans="1:59" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="59"/>
-      <c r="B2" s="59"/>
+    <row r="2" spans="1:59" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
       <c r="C2" s="41" t="s">
         <v>11</v>
       </c>
@@ -15431,9 +15462,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:59" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
+    <row r="3" spans="1:59" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="41">
         <v>31</v>
       </c>
@@ -15599,15 +15630,15 @@
       <c r="BE3" s="3">
         <v>30</v>
       </c>
-      <c r="BF3" s="51">
+      <c r="BF3" s="47">
         <f>SUM(C3:BE3)</f>
         <v>1672</v>
       </c>
-      <c r="BG3" s="52" t="s">
+      <c r="BG3" s="48" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="40" t="s">
         <v>35</v>
@@ -15784,7 +15815,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>28</v>
       </c>
@@ -16019,7 +16050,7 @@
         <v>11042.193548387097</v>
       </c>
     </row>
-    <row r="6" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>28</v>
       </c>
@@ -16237,7 +16268,7 @@
         <v>14738</v>
       </c>
     </row>
-    <row r="7" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>28</v>
       </c>
@@ -16471,7 +16502,7 @@
         <v>15561.58064516129</v>
       </c>
     </row>
-    <row r="8" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>28</v>
       </c>
@@ -16680,7 +16711,7 @@
         <v>19009.322580645163</v>
       </c>
     </row>
-    <row r="9" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>28</v>
       </c>
@@ -16916,7 +16947,7 @@
         <v>14505.566666666668</v>
       </c>
     </row>
-    <row r="10" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
@@ -17136,7 +17167,7 @@
         <v>15972.966666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
@@ -17335,7 +17366,7 @@
         <v>10636.258064516129</v>
       </c>
     </row>
-    <row r="12" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
@@ -17551,7 +17582,7 @@
         <v>16429.333333333332</v>
       </c>
     </row>
-    <row r="13" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>28</v>
       </c>
@@ -17663,7 +17694,7 @@
         <v>12452.366666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
         <v>28</v>
       </c>
@@ -17888,7 +17919,7 @@
         <v>97559.766666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
         <v>40</v>
       </c>
@@ -18120,7 +18151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>29</v>
       </c>
@@ -18288,7 +18319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>29</v>
       </c>
@@ -18515,7 +18546,7 @@
         <v>6634.5</v>
       </c>
     </row>
-    <row r="18" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>29</v>
       </c>
@@ -18737,7 +18768,7 @@
         <v>12098.866666666667</v>
       </c>
     </row>
-    <row r="19" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>29</v>
       </c>
@@ -18963,7 +18994,7 @@
         <v>7060.6</v>
       </c>
     </row>
-    <row r="20" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>29</v>
       </c>
@@ -19150,7 +19181,7 @@
         <v>13107.2</v>
       </c>
     </row>
-    <row r="21" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>29</v>
       </c>
@@ -19328,7 +19359,7 @@
         <v>11041.6</v>
       </c>
     </row>
-    <row r="22" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B22" s="17" t="s">
         <v>29</v>
       </c>
@@ -19553,7 +19584,7 @@
         <v>49942.76666666667</v>
       </c>
     </row>
-    <row r="23" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B23" s="17" t="s">
         <v>40</v>
       </c>
@@ -19781,11 +19812,11 @@
         <f>AVERAGE(C23:BE23)</f>
         <v>4878.7188797700301</v>
       </c>
-      <c r="BG23" s="53" t="s">
+      <c r="BG23" s="49" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B24" s="8" t="s">
         <v>27</v>
       </c>
@@ -20017,18 +20048,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:61" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="BF25" s="54">
+    <row r="25" spans="1:61" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="BF25" s="50">
         <f>BF3*BF24</f>
         <v>173893358.34348866</v>
       </c>
-      <c r="BG25" s="55" t="s">
+      <c r="BG25" s="51" t="s">
         <v>57</v>
       </c>
       <c r="BH25" s="14"/>
       <c r="BI25" s="14"/>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
         <v>30</v>
       </c>
@@ -20068,7 +20099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
         <v>31</v>
       </c>
@@ -20109,7 +20140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:61" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:61" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="32" t="s">
         <v>42</v>
       </c>
@@ -20177,7 +20208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:61" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:61" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="26">
         <f>BE29</f>
         <v>19</v>
@@ -20317,7 +20348,7 @@
         <v>14</v>
       </c>
       <c r="AJ29" s="26">
-        <f t="shared" ref="AJ29:BO29" si="7">AI29+AJ28</f>
+        <f t="shared" ref="AJ29:BE29" si="7">AI29+AJ28</f>
         <v>14</v>
       </c>
       <c r="AK29" s="26">
@@ -20405,7 +20436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A30" s="33">
         <f t="shared" ref="A30:A31" si="8">BE30</f>
         <v>9</v>
@@ -20634,7 +20665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:61" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:61" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A31" s="34">
         <f t="shared" si="8"/>
         <v>10</v>
@@ -20863,374 +20894,414 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:61" s="31" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:61" s="31" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="50">
+      <c r="B32" s="46">
         <v>0.08</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="S32" s="56" t="s">
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="S32" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="T32" s="56"/>
-      <c r="U32" s="56"/>
-      <c r="V32" s="56"/>
-      <c r="W32" s="56"/>
-      <c r="X32" s="56"/>
-      <c r="Y32" s="56"/>
-      <c r="Z32" s="56"/>
-      <c r="AA32" s="56"/>
-      <c r="AB32" s="56"/>
-      <c r="AC32" s="56"/>
-      <c r="AD32" s="56"/>
-      <c r="AE32" s="56"/>
-      <c r="AF32" s="56"/>
-      <c r="AL32" s="57" t="s">
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="52"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="52"/>
+      <c r="AA32" s="52"/>
+      <c r="AB32" s="52"/>
+      <c r="AC32" s="52"/>
+      <c r="AD32" s="52"/>
+      <c r="AE32" s="52"/>
+      <c r="AF32" s="52"/>
+      <c r="AL32" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="AM32" s="57"/>
-      <c r="AN32" s="57"/>
-      <c r="AO32" s="57"/>
-      <c r="AP32" s="57"/>
-      <c r="AQ32" s="57"/>
-      <c r="AR32" s="57"/>
-      <c r="AS32" s="57"/>
-      <c r="AT32" s="57"/>
-      <c r="AU32" s="57"/>
-      <c r="AV32" s="57"/>
-      <c r="AW32" s="57"/>
-      <c r="AX32" s="57"/>
-      <c r="AY32" s="57"/>
+      <c r="AM32" s="53"/>
+      <c r="AN32" s="53"/>
+      <c r="AO32" s="53"/>
+      <c r="AP32" s="53"/>
+      <c r="AQ32" s="53"/>
+      <c r="AR32" s="53"/>
+      <c r="AS32" s="53"/>
+      <c r="AT32" s="53"/>
+      <c r="AU32" s="53"/>
+      <c r="AV32" s="53"/>
+      <c r="AW32" s="53"/>
+      <c r="AX32" s="53"/>
+      <c r="AY32" s="53"/>
       <c r="BF32" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A33" s="47">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A33" s="45">
         <f>NPV(RATE/12,C33:BE33)</f>
         <v>6023132681.805439</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="57">
         <f t="shared" ref="C33:AH33" si="13">C3*(C4-OPEX)*C24</f>
         <v>28065216.091628574</v>
       </c>
-      <c r="D33" s="44">
+      <c r="D33" s="57">
         <f t="shared" si="13"/>
         <v>33149967.283333331</v>
       </c>
-      <c r="E33" s="44">
+      <c r="E33" s="57">
         <f t="shared" si="13"/>
         <v>60259274.363076918</v>
       </c>
-      <c r="F33" s="44">
+      <c r="F33" s="57">
         <f t="shared" si="13"/>
         <v>65509243.205217384</v>
       </c>
-      <c r="G33" s="44">
+      <c r="G33" s="57">
         <f t="shared" si="13"/>
         <v>83616840.719999999</v>
       </c>
-      <c r="H33" s="44">
+      <c r="H33" s="57">
         <f t="shared" si="13"/>
         <v>96467354.346206903</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="57">
         <f t="shared" si="13"/>
         <v>90849203.75999999</v>
       </c>
-      <c r="J33" s="44">
+      <c r="J33" s="57">
         <f t="shared" si="13"/>
         <v>90136887.990612611</v>
       </c>
-      <c r="K33" s="44">
+      <c r="K33" s="57">
         <f t="shared" si="13"/>
         <v>72499845.440000013</v>
       </c>
-      <c r="L33" s="44">
+      <c r="L33" s="57">
         <f t="shared" si="13"/>
         <v>68833223.480000004</v>
       </c>
-      <c r="M33" s="44">
+      <c r="M33" s="57">
         <f t="shared" si="13"/>
         <v>72415497.689999998</v>
       </c>
-      <c r="N33" s="44">
+      <c r="N33" s="57">
         <f t="shared" si="13"/>
         <v>57489223.821839087</v>
       </c>
-      <c r="O33" s="44">
+      <c r="O33" s="57">
         <f t="shared" si="13"/>
         <v>50842803.960000001</v>
       </c>
-      <c r="P33" s="44">
+      <c r="P33" s="57">
         <f t="shared" si="13"/>
         <v>34507956.299999997</v>
       </c>
-      <c r="Q33" s="44">
+      <c r="Q33" s="57">
         <f t="shared" si="13"/>
         <v>34259768.325517237</v>
       </c>
-      <c r="R33" s="44">
+      <c r="R33" s="57">
         <f t="shared" si="13"/>
         <v>52610687.249999993</v>
       </c>
-      <c r="S33" s="44">
+      <c r="S33" s="57">
         <f t="shared" si="13"/>
         <v>62903416.02387096</v>
       </c>
-      <c r="T33" s="44">
+      <c r="T33" s="57">
         <f t="shared" si="13"/>
         <v>82623476.122400001</v>
       </c>
-      <c r="U33" s="44">
+      <c r="U33" s="57">
         <f t="shared" si="13"/>
         <v>96805428.363636374</v>
       </c>
-      <c r="V33" s="44">
+      <c r="V33" s="57">
         <f t="shared" si="13"/>
         <v>87931942.099999994</v>
       </c>
-      <c r="W33" s="44">
+      <c r="W33" s="57">
         <f t="shared" si="13"/>
         <v>95870942.228571445</v>
       </c>
-      <c r="X33" s="44">
+      <c r="X33" s="57">
         <f t="shared" si="13"/>
         <v>97752969.159999996</v>
       </c>
-      <c r="Y33" s="44">
+      <c r="Y33" s="57">
         <f t="shared" si="13"/>
         <v>110962814.00000001</v>
       </c>
-      <c r="Z33" s="44">
+      <c r="Z33" s="57">
         <f t="shared" si="13"/>
         <v>89353418.121206895</v>
       </c>
-      <c r="AA33" s="44">
+      <c r="AA33" s="57">
         <f t="shared" si="13"/>
         <v>128780175.98999999</v>
       </c>
-      <c r="AB33" s="44">
+      <c r="AB33" s="57">
         <f t="shared" si="13"/>
         <v>134856353.27466667</v>
       </c>
-      <c r="AC33" s="44">
+      <c r="AC33" s="57">
         <f t="shared" si="13"/>
         <v>119752694.73</v>
       </c>
-      <c r="AD33" s="44">
+      <c r="AD33" s="57">
         <f t="shared" si="13"/>
         <v>125660546.95535716</v>
       </c>
-      <c r="AE33" s="44">
+      <c r="AE33" s="57">
         <f t="shared" si="13"/>
         <v>127445997.77000003</v>
       </c>
-      <c r="AF33" s="44">
+      <c r="AF33" s="57">
         <f t="shared" si="13"/>
         <v>134201564.70157897</v>
       </c>
-      <c r="AG33" s="44">
+      <c r="AG33" s="57">
         <f t="shared" si="13"/>
         <v>116056922.54999998</v>
       </c>
-      <c r="AH33" s="44">
+      <c r="AH33" s="57">
         <f t="shared" si="13"/>
         <v>127898145.19862068</v>
       </c>
-      <c r="AI33" s="44">
+      <c r="AI33" s="57">
         <f t="shared" ref="AI33:BE33" si="14">AI3*(AI4-OPEX)*AI24</f>
         <v>125273894.80586208</v>
       </c>
-      <c r="AJ33" s="44">
+      <c r="AJ33" s="57">
         <f t="shared" si="14"/>
         <v>136679889.59999999</v>
       </c>
-      <c r="AK33" s="44">
+      <c r="AK33" s="57">
         <f t="shared" si="14"/>
         <v>140338340.42892855</v>
       </c>
-      <c r="AL33" s="44">
+      <c r="AL33" s="57">
         <f t="shared" si="14"/>
         <v>165692447.49571428</v>
       </c>
-      <c r="AM33" s="44">
+      <c r="AM33" s="57">
         <f t="shared" si="14"/>
         <v>169946844.70000005</v>
       </c>
-      <c r="AN33" s="44">
+      <c r="AN33" s="57">
         <f t="shared" si="14"/>
         <v>188221301.94758618</v>
       </c>
-      <c r="AO33" s="44">
+      <c r="AO33" s="57">
         <f t="shared" si="14"/>
         <v>163875684.71999997</v>
       </c>
-      <c r="AP33" s="44">
+      <c r="AP33" s="57">
         <f t="shared" si="14"/>
         <v>188385074.53999999</v>
       </c>
-      <c r="AQ33" s="44">
+      <c r="AQ33" s="57">
         <f t="shared" si="14"/>
         <v>201254093.95071426</v>
       </c>
-      <c r="AR33" s="44">
+      <c r="AR33" s="57">
         <f t="shared" si="14"/>
         <v>251228492.40000001</v>
       </c>
-      <c r="AS33" s="44">
+      <c r="AS33" s="57">
         <f t="shared" si="14"/>
         <v>248961367.63333333</v>
       </c>
-      <c r="AT33" s="44">
+      <c r="AT33" s="57">
         <f t="shared" si="14"/>
         <v>265016540.24999997</v>
       </c>
-      <c r="AU33" s="44">
+      <c r="AU33" s="57">
         <f t="shared" si="14"/>
         <v>266906580.49000001</v>
       </c>
-      <c r="AV33" s="44">
+      <c r="AV33" s="57">
         <f t="shared" si="14"/>
         <v>282162709.87</v>
       </c>
-      <c r="AW33" s="44">
+      <c r="AW33" s="57">
         <f t="shared" si="14"/>
         <v>291742990.20000005</v>
       </c>
-      <c r="AX33" s="44">
+      <c r="AX33" s="57">
         <f t="shared" si="14"/>
         <v>212072172.75862068</v>
       </c>
-      <c r="AY33" s="44">
+      <c r="AY33" s="57">
         <f t="shared" si="14"/>
         <v>194949423.19471261</v>
       </c>
-      <c r="AZ33" s="44">
+      <c r="AZ33" s="57">
         <f t="shared" si="14"/>
         <v>211723209.46999997</v>
       </c>
-      <c r="BA33" s="44">
+      <c r="BA33" s="57">
         <f t="shared" si="14"/>
         <v>207292821.12</v>
       </c>
-      <c r="BB33" s="44">
+      <c r="BB33" s="57">
         <f t="shared" si="14"/>
         <v>234941830.78666666</v>
       </c>
-      <c r="BC33" s="44">
+      <c r="BC33" s="57">
         <f t="shared" si="14"/>
         <v>250512859.57999995</v>
       </c>
-      <c r="BD33" s="44">
+      <c r="BD33" s="57">
         <f t="shared" si="14"/>
         <v>252773617.86434776</v>
       </c>
-      <c r="BE33" s="49">
+      <c r="BE33" s="58">
         <f t="shared" si="14"/>
         <v>217802240.71999997</v>
       </c>
-      <c r="BF33" s="48">
+      <c r="BF33" s="59">
         <f>SUM(C33:BE33)</f>
         <v>7598124229.8438263</v>
       </c>
-      <c r="BG33" s="19" t="s">
+      <c r="BG33" s="60" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A34" s="47">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A34" s="45">
         <f>-NPV(RATE/12,C34:BE34)</f>
         <v>-9722880633.6789722</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="48">
+      <c r="C34" s="59">
         <f>A41+C26*MALOcost+C27*JACKcost</f>
         <v>5300000000</v>
       </c>
-      <c r="D34" s="48">
+      <c r="D34" s="59">
         <f>D26*MALOcost+D27*JACKcost</f>
         <v>1000000000</v>
       </c>
-      <c r="E34" s="48">
+      <c r="E34" s="59">
         <f>E26*MALOcost+E27*JACKcost</f>
         <v>300000000</v>
       </c>
-      <c r="G34" s="48">
+      <c r="F34" s="60"/>
+      <c r="G34" s="59">
         <f>G26*MALOcost+G27*RecompCOST</f>
         <v>100000000</v>
       </c>
-      <c r="J34" s="48">
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="59">
         <f>J26*MALOcost+J27*RecompCOST</f>
         <v>100000000</v>
       </c>
-      <c r="S34" s="48">
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="60"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="59">
         <f>S26*MALOcost+S27*JACKcost</f>
         <v>300000000</v>
       </c>
-      <c r="U34" s="48">
+      <c r="T34" s="60"/>
+      <c r="U34" s="59">
         <f>U26*MALOcost+U27*JACKcost</f>
         <v>300000000</v>
       </c>
-      <c r="W34" s="48">
+      <c r="V34" s="60"/>
+      <c r="W34" s="59">
         <f>W26*MALOcost+W27*JACKcost</f>
         <v>300000000</v>
       </c>
-      <c r="AB34" s="48">
+      <c r="X34" s="60"/>
+      <c r="Y34" s="60"/>
+      <c r="Z34" s="60"/>
+      <c r="AA34" s="60"/>
+      <c r="AB34" s="59">
         <f>AB26*MALOcost+AB27*RecompCOST</f>
         <v>100000000</v>
       </c>
-      <c r="AF34" s="48">
+      <c r="AC34" s="60"/>
+      <c r="AD34" s="60"/>
+      <c r="AE34" s="60"/>
+      <c r="AF34" s="59">
         <f>AF26*MALOcost+AF27*JACKcost</f>
         <v>300000000</v>
       </c>
-      <c r="AL34" s="45">
+      <c r="AG34" s="60"/>
+      <c r="AH34" s="60"/>
+      <c r="AI34" s="60"/>
+      <c r="AJ34" s="60"/>
+      <c r="AK34" s="60"/>
+      <c r="AL34" s="61">
         <f>A42+AL27*JACKcost</f>
         <v>850000000</v>
       </c>
-      <c r="AN34" s="48">
+      <c r="AM34" s="60"/>
+      <c r="AN34" s="59">
         <f>AN26*MALOcost+AN27*JACKcost</f>
         <v>300000000</v>
       </c>
-      <c r="AQ34" s="48">
+      <c r="AO34" s="60"/>
+      <c r="AP34" s="60"/>
+      <c r="AQ34" s="59">
         <f>AQ26*MALOcost+AQ27*RecompCOST</f>
         <v>100000000</v>
       </c>
-      <c r="AS34" s="48">
+      <c r="AR34" s="60"/>
+      <c r="AS34" s="59">
         <f>AS26*MALOcost+AS27*JACKcost</f>
         <v>300000000</v>
       </c>
-      <c r="AY34" s="48">
+      <c r="AT34" s="60"/>
+      <c r="AU34" s="60"/>
+      <c r="AV34" s="60"/>
+      <c r="AW34" s="60"/>
+      <c r="AX34" s="60"/>
+      <c r="AY34" s="59">
         <f>AY26*MALOcost+AY27*JACKcost</f>
         <v>350000000</v>
       </c>
-      <c r="BF34" s="48">
+      <c r="AZ34" s="60"/>
+      <c r="BA34" s="60"/>
+      <c r="BB34" s="60"/>
+      <c r="BC34" s="60"/>
+      <c r="BD34" s="60"/>
+      <c r="BE34" s="60"/>
+      <c r="BF34" s="59">
         <f>SUM(C34:BE34)</f>
         <v>10000000000</v>
       </c>
-      <c r="BG34" s="19" t="s">
+      <c r="BG34" s="60" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A35" s="46">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A35" s="44">
         <f>A33+A34</f>
         <v>-3699747951.8735332</v>
       </c>
@@ -21238,13 +21309,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:59" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A36" s="60" t="s">
+    <row r="36" spans="1:59" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A36" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="60"/>
+      <c r="B36" s="56"/>
     </row>
-    <row r="37" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A37" s="42">
         <v>15</v>
       </c>
@@ -21252,7 +21323,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A38" s="43">
         <v>300000000</v>
       </c>
@@ -21260,7 +21331,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A39" s="43">
         <v>350000000</v>
       </c>
@@ -21268,7 +21339,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A40" s="43">
         <v>100000000</v>
       </c>
@@ -21276,7 +21347,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A41" s="43">
         <v>4300000000</v>
       </c>
@@ -21284,7 +21355,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A42" s="43">
         <v>500000000</v>
       </c>
